--- a/Result/profitability/8050.xlsx
+++ b/Result/profitability/8050.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.15</v>
       </c>
       <c r="M2" t="n">
-        <v>0.65</v>
+        <v>0.775</v>
       </c>
       <c r="N2" t="n">
-        <v>23.415</v>
+        <v>23.57125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.755</v>
+        <v>0.845</v>
       </c>
       <c r="N3" t="n">
-        <v>24.845</v>
+        <v>25.51</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -801,7 +801,7 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.66</v>
       </c>
       <c r="M4" t="n">
-        <v>0.85</v>
+        <v>0.9125</v>
       </c>
       <c r="N4" t="n">
-        <v>27.16875</v>
+        <v>27.6025</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.75</v>
       </c>
       <c r="M5" t="n">
-        <v>0.80375</v>
+        <v>1.08625</v>
       </c>
       <c r="N5" t="n">
-        <v>29.1575</v>
+        <v>29.55375</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,13 +1036,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.89</v>
       </c>
       <c r="M6" t="n">
-        <v>0.995</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>31.45625</v>
+        <v>32.10375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.95</v>
+        <v>1.1375</v>
       </c>
       <c r="N7" t="n">
-        <v>33.63125</v>
+        <v>34.53375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0175</v>
+        <v>1.08625</v>
       </c>
       <c r="N8" t="n">
-        <v>36.41875</v>
+        <v>36.74</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>0.83</v>
       </c>
       <c r="N12" t="n">
-        <v>37.19625000000001</v>
+        <v>37.19625</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8050</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2105</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E75" t="n">
+        <v>545</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="G75" t="n">
+        <v>182</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>69</v>
+      </c>
+      <c r="J75" t="n">
+        <v>251</v>
+      </c>
+      <c r="K75" t="n">
+        <v>239</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.70875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.3475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.514018691588785</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1103004291845493</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.53125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.170000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1396475770925112</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
